--- a/submissions/methods_description_gummietech.xlsx
+++ b/submissions/methods_description_gummietech.xlsx
@@ -933,10 +933,17 @@
 aneuploidy" is an HSP90 inhibitor — which is predicted to **destroy the residual BubR1 this
 child depends on**, because mutant BubR1 is an HSP90 client.
 ### Describe manual literature review and expert curation
-Thirty-four sources captured in full text in `literature/`, each with verbatim quotes, an
-explicit **LIMITS** section stating what the paper does *not* show, and an evidence tier
-(human RCT / human phase 1–2 / observational human / mouse in the BubR1 background / mouse
-elsewhere / cell line / in silico). Supporting registers: a **claims register** grading
+**31 source files** in `literature/` — 24 of them primary literature, the remainder site
+captures, tool documentation, clinical guidelines and a bibliography — each captured with
+verbatim quotes and its acquisition provenance logged. Most are full text; those obtainable
+only as abstracts are **labelled abstract-only** rather than presented as full text, and the
+fetch log records which.
+The **LIMITS** convention (an explicit section stating what a paper does *not* show) and the
+evidence tier (human RCT / human phase 1–2 / observational human / mouse in the BubR1
+background / mouse elsewhere / cell line / in silico) were introduced with the adversarial
+review pass and apply to the **10 files added under it**, not retroactively to the earlier
+corpus. Stated precisely because an earlier draft of this form claimed all of them carried
+it — which is not true, and is checkable in one command. Supporting registers: a **claims register** grading
 every assertion, a **contradiction matrix** adjudicating 19 conflicts with grounds, an
 **open-questions file** ranking what the literature cannot answer by decision value, and a
 **fetch log** recording every acquisition attempt including failures.
@@ -1060,7 +1067,8 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thirty-four sources captured in full text in literature/, each with verbatim quotes, an explicit LIMITS section stating what the paper does not show, and an evidence tier (human RCT / human phase 1–2 / observational human / mouse in the BubR1 background / mouse elsewhere / cell line / in silico). Supporting registers: a claims register grading every assertion, a contradiction matrix adjudicating 19 conflicts with grounds, an open-questions file ranking what the literature cannot answer by decision value, and a fetch log recording every acquisition attempt including failures.
+          <t xml:space="preserve">31 source files in literature/ — 24 of them primary literature, the remainder site captures, tool documentation, clinical guidelines and a bibliography — each captured with verbatim quotes and its acquisition provenance logged. Most are full text; those obtainable only as abstracts are labelled abstract-only rather than presented as full text, and the fetch log records which.
+The LIMITS convention (an explicit section stating what a paper does not show) and the evidence tier (human RCT / human phase 1–2 / observational human / mouse in the BubR1 background / mouse elsewhere / cell line / in silico) were introduced with the adversarial review pass and apply to the 10 files added under it, not retroactively to the earlier corpus. Stated precisely because an earlier draft of this form claimed all of them carried it — which is not true, and is checkable in one command. Supporting registers: a claims register grading every assertion, a contradiction matrix adjudicating 19 conflicts with grounds, an open-questions file ranking what the literature cannot answer by decision value, and a fetch log recording every acquisition attempt including failures.
 An adversarial review pass was run against the submission's own thesis. It found, among other things, that HSP90 inhibitors are also a recognised senolytic class — meaning the top approved-medication tier contained its own hard contraindication, reachable without ever mentioning aneuploidy, and that "senolytic" cannot be used as a class-level safety label in this child.</t>
         </is>
       </c>

--- a/submissions/methods_description_gummietech.xlsx
+++ b/submissions/methods_description_gummietech.xlsx
@@ -714,7 +714,7 @@
 That limitation is *open, not unclosable* — a reduced-reference realignment would close it
 at named costs, and BUB1B carries zero segmental duplications, so the route is sound for
 this gene specifically. CNVs are not called at all; a multi-exon deletion remains possible
-in five named windows. Phase is unresolved. `p.Asn1002Lys` remains a VUS and this
+in six named windows, three of them in-frame. Phase is unresolved. `p.Asn1002Lys` remains a VUS and this
 submission does not upgrade it.
 ---</t>
         </is>
@@ -844,7 +844,7 @@
           <t xml:space="preserve">We recover a compound-heterozygous BUB1B candidate — p.Leu737Ter (ClinVar Pathogenic/Likely pathogenic) plus p.Asn1002Lys (gnomAD singleton, VUS) — from the proband's own VCF using a four-stage pipeline: Ensembl-REST coordinate resolution into a padded BED, bcftools region restriction, VEP REST annotation with the SpliceAI plugin, and a rare/damaging filter. All code is CLI-parameterised and standard-library only.
 The submission's distinguishing feature is not the variant call, which the public leaderboard shows the field has converged on. It is the verification discipline applied to it. Every population-frequency, clinical-classification, domain and predictor claim was re-derived from its primary source rather than taken from the annotation tool, and that process repeatedly found real errors — including a rarity filter that silently excluded gnomAD exome frequencies (proved harmless by replaying the corrected filter against saved raw responses: identical candidate set), a callability ratio that contradicted the report's own prose, and a PP4 argument resting on a claim this repository's own captured literature disproves. Roughly sixty figures were re-derived from primary artefacts; six were wrong and are corrected in place, with the corrections recorded rather than quietly absorbed.
 Strengths. Reproducible from code and documented commands. Evidence codes tested and rejected where unsupported — PM1 is rejected on gnomAD missense density in the very domain that would otherwise support it, and PS4 was dropped as improperly applied. Negative results are reported as negatives. The phasing limitation is stated, not assumed away.
-Limitations, and they are load-bearing. The search space is a literature-defined MVA panel, so this cannot distinguish discovery from confirmation, and no such claim is made. The input is a sites-only VCF: absence of a call and absence of coverage are indistinguishable, and every negative in the report rests on that undifferentiated absence. A call-density-against-flanking-sequence proxy is offered and explicitly labelled a proxy. That limitation is open, not unclosable — a reduced-reference realignment would close it at named costs, and BUB1B carries zero segmental duplications, so the route is sound for this gene specifically. CNVs are not called at all; a multi-exon deletion remains possible in five named windows. Phase is unresolved. p.Asn1002Lys remains a VUS and this submission does not upgrade it.
+Limitations, and they are load-bearing. The search space is a literature-defined MVA panel, so this cannot distinguish discovery from confirmation, and no such claim is made. The input is a sites-only VCF: absence of a call and absence of coverage are indistinguishable, and every negative in the report rests on that undifferentiated absence. A call-density-against-flanking-sequence proxy is offered and explicitly labelled a proxy. That limitation is open, not unclosable — a reduced-reference realignment would close it at named costs, and BUB1B carries zero segmental duplications, so the route is sound for this gene specifically. CNVs are not called at all; a multi-exon deletion remains possible in six named windows, three of them in-frame. Phase is unresolved. p.Asn1002Lys remains a VUS and this submission does not upgrade it.
 ---</t>
         </is>
       </c>
@@ -984,48 +984,51 @@
   buried than Asn1002. That is reported as the result it is, and the report's Limitation 1
   is tightened rather than relaxed.
 ### Time or effort
-2026-08-31 to 2026-09-04, 32 commits. The mechanism characterisation and the verification
+2026-08-31 to 2026-09-04, 39 commits. The mechanism characterisation and the verification
 passes consumed substantially more effort than the drug search itself, which is the correct
 ratio for this problem: the search is cheap and the reframing is what makes it point
 anywhere useful.
 ### Method abstract (≤500 words)
-BUB1B has **zero** drugs in Open Targets and DGIdb independently, and so does every other
-spindle-assembly-checkpoint gene. Rather than treat that as failure, we treat it as
-information and ask what the shape of the surrounding pharmacopeia reveals.
-Across 24 pathway genes and two databases, **drug availability rises monotonically with
-distance from the defect** (0 at BUB1B, 71 at the SASP tier), and **129 of 142 action-typed
-Open Targets entries are inhibitors** — ~95% inhibitory against a disease of deficiency.
-That mismatch is the submission's generalisable finding: medicine is built out of
-inhibitors, and loss-of-function rare disease needs the opposite. We pre-registered a
-falsifiable version of that claim and tested it on three further genes, including one
-(CFTR) chosen because the prediction should *fail* there.
+BUB1B has **zero** drugs in Open Targets and DGIdb independently, as does every other
+spindle-assembly-checkpoint gene. Rather than treat that as failure we treat it as
+information, and ask what the surrounding pharmacopeia's shape reveals.
+Across 24 pathway genes and two databases, **129 of 142 action-typed Open Targets entries
+are inhibitors** — ~95% inhibitory against a disease of deficiency. We pre-registered a
+falsifiable version of that mismatch, with its withdrawal criterion, and tested it on three
+further genes including one (CFTR) chosen because it should *fail* there. **Two of three
+predictions failed and the generalisation is withdrawn.** The skew does not track
+loss-of-function (NPC1 **54.5%**, CFTR **37.5%**) but whether the causal gene sits in a
+pathway oncology has invested in inhibiting (BUB1B **95.8%**, ATM **93.4%**) — narrower, and
+diagnostic: it says in advance which rare diseases face this problem, and BUB1B is in the
+worst category. Our monotonic-rise-with-distance claim likewise failed under a mechanical
+STRING tier rule, for BUB1B itself (0 → 375 → 198), and is reported as an artefact of our
+own curation. What survives both tests is **the zero at the defect**.
 **Ranked answer, with regulatory status never blurred.** Highest overall: nicotinamide
 riboside (13/17) — a **dietary supplement, not an approved medicine**. Highest approved
 medication: dasatinib + quercetin (10/17), where **none of 22 trials ever enrolled a
-child**. Three agents are excluded by gates fixed before the search, including HSP90
-inhibitors — simultaneously the lead compound of the best-known "drugs for aneuploidy"
-paper and, here, predicted to destroy the residual protein the child depends on.
-**What we actually recommend first is not a drug.** It is a western blot for BubR1, which
-forks the entire hypothesis and would additionally generate PS3-grade functional evidence
-on Track 1's unresolved VUS. Measure before treating.
+child**. Gates fixed before the search exclude HSP90 inhibitors — simultaneously the lead
+compound of the best-known "drugs for aneuploidy" paper and, here, predicted to destroy the
+residual protein the child depends on.
+**What we recommend first is not a drug.** It is a western blot for BubR1, which forks the
+entire hypothesis and would additionally generate PS3-grade functional evidence on Track 1's
+unresolved VUS. Measure before treating.
 **A patient-specific layer.** A CPIC-guided PharmCAT screen of the proband's own genome,
-whose headline is an honest negative: only 22 of 1,226 positions carry a call, and **16 of
-23 genes change call** when absent positions are assumed reference — an assumption
-PharmCAT's own CLI labels "DANGEROUS!". It also caught a false alarm worth catching:
-PharmCAT reports RYR1 `rs35364374` as "Uncertain Susceptibility" to malignant hyperthermia,
-while ClinGen's expert panel classifies that exact variant **Benign**.
+whose headline is an honest negative: only 22 of 1,226 positions carry an interpretable
+call, and **16 of 23 genes change call** when absent positions are assumed reference — an
+assumption PharmCAT's own CLI labels "DANGEROUS!". It also caught a false alarm: PharmCAT
+reports RYR1 `rs35364374` as "Uncertain Susceptibility" to malignant hyperthermia; ClinGen's
+expert panel classifies that variant **Benign**.
 **Strengths.** Pre-registration verifiable from commit order. Two independent drug
-databases. Paediatric eligibility from structured fields. Mechanism-derived exclusion gates
-that catch a contraindication no pathway search surfaces. Twenty-six verification findings
-that each *changed* the submission, several against its own thesis.
+databases. Mechanism-derived gates catching a contraindication no pathway search surfaces.
+**Forty-two verification findings that each *changed* the submission**, several against its
+own thesis. A closing audit re-derived every figure above from the artefacts; all reproduce.
 **Limitations.** No NAD⁺ precursor has been given to a BubR1-deficient animal, let alone a
-person with MVA; the lead candidate's central inference is untested. The mouse models the
-report draws on **do not carry the human MVA genotype** — the mouse built with the patient
-architecture is embryonic lethal where the equivalent human lived. Human NAD⁺ trials have
-failed on musculoskeletal endpoints. `p.Asn1002Lys` is not proven to destabilise BubR1, and
-structural analysis made that analogy weaker rather than stronger. n = 1. Nothing here is
-medical advice, and no MVA patient has ever received any of these agents for this
-indication.</t>
+person with MVA; the lead candidate's central inference is untested. The mouse models **do
+not carry the human MVA genotype** — the mouse built with the patient architecture is
+embryonic lethal where the equivalent human lived. Human NAD⁺ trials have failed on
+musculoskeletal endpoints. `p.Asn1002Lys` is not proven to destabilise BubR1, and structural
+analysis made that analogy weaker, not stronger. n = 1. No MVA patient has ever received any
+of these agents for this indication, and nothing here is medical advice.</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1129,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31 to 2026-09-04, 32 commits. The mechanism characterisation and the verification passes consumed substantially more effort than the drug search itself, which is the correct ratio for this problem: the search is cheap and the reframing is what makes it point anywhere useful.</t>
+          <t xml:space="preserve">2026-08-31 to 2026-09-04, 39 commits. The mechanism characterisation and the verification passes consumed substantially more effort than the drug search itself, which is the correct ratio for this problem: the search is cheap and the reframing is what makes it point anywhere useful.</t>
         </is>
       </c>
     </row>
@@ -1136,13 +1139,13 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUB1B has zero drugs in Open Targets and DGIdb independently, and so does every other spindle-assembly-checkpoint gene. Rather than treat that as failure, we treat it as information and ask what the shape of the surrounding pharmacopeia reveals.
-Across 24 pathway genes and two databases, drug availability rises monotonically with distance from the defect (0 at BUB1B, 71 at the SASP tier), and 129 of 142 action-typed Open Targets entries are inhibitors — ~95% inhibitory against a disease of deficiency. That mismatch is the submission's generalisable finding: medicine is built out of inhibitors, and loss-of-function rare disease needs the opposite. We pre-registered a falsifiable version of that claim and tested it on three further genes, including one (CFTR) chosen because the prediction should fail there.
-Ranked answer, with regulatory status never blurred. Highest overall: nicotinamide riboside (13/17) — a dietary supplement, not an approved medicine. Highest approved medication: dasatinib + quercetin (10/17), where none of 22 trials ever enrolled a child. Three agents are excluded by gates fixed before the search, including HSP90 inhibitors — simultaneously the lead compound of the best-known "drugs for aneuploidy" paper and, here, predicted to destroy the residual protein the child depends on.
-What we actually recommend first is not a drug. It is a western blot for BubR1, which forks the entire hypothesis and would additionally generate PS3-grade functional evidence on Track 1's unresolved VUS. Measure before treating.
-A patient-specific layer. A CPIC-guided PharmCAT screen of the proband's own genome, whose headline is an honest negative: only 22 of 1,226 positions carry a call, and 16 of 23 genes change call when absent positions are assumed reference — an assumption PharmCAT's own CLI labels "DANGEROUS!". It also caught a false alarm worth catching: PharmCAT reports RYR1 rs35364374 as "Uncertain Susceptibility" to malignant hyperthermia, while ClinGen's expert panel classifies that exact variant Benign.
-Strengths. Pre-registration verifiable from commit order. Two independent drug databases. Paediatric eligibility from structured fields. Mechanism-derived exclusion gates that catch a contraindication no pathway search surfaces. Twenty-six verification findings that each changed the submission, several against its own thesis.
-Limitations. No NAD⁺ precursor has been given to a BubR1-deficient animal, let alone a person with MVA; the lead candidate's central inference is untested. The mouse models the report draws on do not carry the human MVA genotype — the mouse built with the patient architecture is embryonic lethal where the equivalent human lived. Human NAD⁺ trials have failed on musculoskeletal endpoints. p.Asn1002Lys is not proven to destabilise BubR1, and structural analysis made that analogy weaker rather than stronger. n = 1. Nothing here is medical advice, and no MVA patient has ever received any of these agents for this indication.</t>
+          <t xml:space="preserve">BUB1B has zero drugs in Open Targets and DGIdb independently, as does every other spindle-assembly-checkpoint gene. Rather than treat that as failure we treat it as information, and ask what the surrounding pharmacopeia's shape reveals.
+Across 24 pathway genes and two databases, 129 of 142 action-typed Open Targets entries are inhibitors — ~95% inhibitory against a disease of deficiency. We pre-registered a falsifiable version of that mismatch, with its withdrawal criterion, and tested it on three further genes including one (CFTR) chosen because it should fail there. Two of three predictions failed and the generalisation is withdrawn. The skew does not track loss-of-function (NPC1 54.5%, CFTR 37.5%) but whether the causal gene sits in a pathway oncology has invested in inhibiting (BUB1B 95.8%, ATM 93.4%) — narrower, and diagnostic: it says in advance which rare diseases face this problem, and BUB1B is in the worst category. Our monotonic-rise-with-distance claim likewise failed under a mechanical STRING tier rule, for BUB1B itself (0 → 375 → 198), and is reported as an artefact of our own curation. What survives both tests is the zero at the defect.
+Ranked answer, with regulatory status never blurred. Highest overall: nicotinamide riboside (13/17) — a dietary supplement, not an approved medicine. Highest approved medication: dasatinib + quercetin (10/17), where none of 22 trials ever enrolled a child. Gates fixed before the search exclude HSP90 inhibitors — simultaneously the lead compound of the best-known "drugs for aneuploidy" paper and, here, predicted to destroy the residual protein the child depends on.
+What we recommend first is not a drug. It is a western blot for BubR1, which forks the entire hypothesis and would additionally generate PS3-grade functional evidence on Track 1's unresolved VUS. Measure before treating.
+A patient-specific layer. A CPIC-guided PharmCAT screen of the proband's own genome, whose headline is an honest negative: only 22 of 1,226 positions carry an interpretable call, and 16 of 23 genes change call when absent positions are assumed reference — an assumption PharmCAT's own CLI labels "DANGEROUS!". It also caught a false alarm: PharmCAT reports RYR1 rs35364374 as "Uncertain Susceptibility" to malignant hyperthermia; ClinGen's expert panel classifies that variant Benign.
+Strengths. Pre-registration verifiable from commit order. Two independent drug databases. Mechanism-derived gates catching a contraindication no pathway search surfaces. Forty-two verification findings that each changed the submission, several against its own thesis. A closing audit re-derived every figure above from the artefacts; all reproduce.
+Limitations. No NAD⁺ precursor has been given to a BubR1-deficient animal, let alone a person with MVA; the lead candidate's central inference is untested. The mouse models do not carry the human MVA genotype — the mouse built with the patient architecture is embryonic lethal where the equivalent human lived. Human NAD⁺ trials have failed on musculoskeletal endpoints. p.Asn1002Lys is not proven to destabilise BubR1, and structural analysis made that analogy weaker, not stronger. n = 1. No MVA patient has ever received any of these agents for this indication, and nothing here is medical advice.</t>
         </is>
       </c>
     </row>

--- a/submissions/methods_description_gummietech.xlsx
+++ b/submissions/methods_description_gummietech.xlsx
@@ -682,7 +682,7 @@
 The full pipeline runs in **under 10 minutes end to end** on a 2019-class laptop (8 GB RAM,
 8 cores), dominated by Ensembl VEP REST latency, not compute. Standard library Python only,
 no cluster, no paid compute. **The analysis time is the cost**: the work spans 2026-08-31
-to 2026-09-04 across 32 commits, the large majority of it verification and audit rather
+to 2026-09-04 across 40 commits, the large majority of it verification and audit rather
 than the initial pipeline, which was the smaller part of the effort.
 ### Method abstract (≤500 words)
 We recover a compound-heterozygous BUB1B candidate — `p.Leu737Ter` (ClinVar
@@ -831,7 +831,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The full pipeline runs in under 10 minutes end to end on a 2019-class laptop (8 GB RAM, 8 cores), dominated by Ensembl VEP REST latency, not compute. Standard library Python only, no cluster, no paid compute. The analysis time is the cost: the work spans 2026-08-31 to 2026-09-04 across 32 commits, the large majority of it verification and audit rather than the initial pipeline, which was the smaller part of the effort.</t>
+          <t xml:space="preserve">The full pipeline runs in under 10 minutes end to end on a 2019-class laptop (8 GB RAM, 8 cores), dominated by Ensembl VEP REST latency, not compute. Standard library Python only, no cluster, no paid compute. The analysis time is the cost: the work spans 2026-08-31 to 2026-09-04 across 40 commits, the large majority of it verification and audit rather than the initial pipeline, which was the smaller part of the effort.</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
   buried than Asn1002. That is reported as the result it is, and the report's Limitation 1
   is tightened rather than relaxed.
 ### Time or effort
-2026-08-31 to 2026-09-04, 39 commits. The mechanism characterisation and the verification
+2026-08-31 to 2026-09-04, 40 commits. The mechanism characterisation and the verification
 passes consumed substantially more effort than the drug search itself, which is the correct
 ratio for this problem: the search is cheap and the reframing is what makes it point
 anywhere useful.
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31 to 2026-09-04, 39 commits. The mechanism characterisation and the verification passes consumed substantially more effort than the drug search itself, which is the correct ratio for this problem: the search is cheap and the reframing is what makes it point anywhere useful.</t>
+          <t xml:space="preserve">2026-08-31 to 2026-09-04, 40 commits. The mechanism characterisation and the verification passes consumed substantially more effort than the drug search itself, which is the correct ratio for this problem: the search is cheap and the reframing is what makes it point anywhere useful.</t>
         </is>
       </c>
     </row>
